--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484577_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484577_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.5554</v>
+        <v>7.6704</v>
       </c>
       <c r="E2" t="n">
-        <v>3.3337</v>
+        <v>3.6222</v>
       </c>
       <c r="F2" t="n">
-        <v>4.2217</v>
+        <v>4.0483</v>
       </c>
       <c r="G2" t="n">
         <v>6.1386</v>
@@ -610,13 +610,13 @@
         <v>1.8326</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7833</v>
+        <v>0.8984</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.2398</v>
+        <v>0.0487</v>
       </c>
       <c r="U2" t="n">
-        <v>1.0231</v>
+        <v>0.8497</v>
       </c>
       <c r="V2" t="n">
         <v>0.6335</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.0983</v>
+        <v>6.2</v>
       </c>
       <c r="E3" t="n">
-        <v>2.9206</v>
+        <v>3.0718</v>
       </c>
       <c r="F3" t="n">
-        <v>3.1778</v>
+        <v>3.1282</v>
       </c>
       <c r="G3" t="n">
         <v>3.4634</v>
@@ -688,13 +688,13 @@
         <v>2.3823</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7369</v>
+        <v>0.8386</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0159</v>
+        <v>0.1671</v>
       </c>
       <c r="U3" t="n">
-        <v>0.7211</v>
+        <v>0.6715</v>
       </c>
       <c r="V3" t="n">
         <v>-0.3011</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>6.0663</v>
+        <v>6.1742</v>
       </c>
       <c r="E4" t="n">
-        <v>3.1487</v>
+        <v>2.8602</v>
       </c>
       <c r="F4" t="n">
-        <v>2.9176</v>
+        <v>3.314</v>
       </c>
       <c r="G4" t="n">
         <v>3.6175</v>
@@ -766,13 +766,13 @@
         <v>1.8326</v>
       </c>
       <c r="S4" t="n">
-        <v>1.0327</v>
+        <v>1.1406</v>
       </c>
       <c r="T4" t="n">
-        <v>0.7119</v>
+        <v>0.4235</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3208</v>
+        <v>0.7171999999999999</v>
       </c>
       <c r="V4" t="n">
         <v>1.5993</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.1072</v>
+        <v>3.2689</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.8639</v>
+        <v>-0.4792</v>
       </c>
       <c r="F5" t="n">
-        <v>3.9711</v>
+        <v>3.7481</v>
       </c>
       <c r="G5" t="n">
         <v>0.0454</v>
@@ -844,13 +844,13 @@
         <v>2.0158</v>
       </c>
       <c r="S5" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.7287</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.5701000000000001</v>
+        <v>-0.1855</v>
       </c>
       <c r="U5" t="n">
-        <v>1.1371</v>
+        <v>0.9142</v>
       </c>
       <c r="V5" t="n">
         <v>1.5785</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. MUÑOZ TORREGROSA</t>
+          <t>D. HOYAS PEREZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6502</v>
+        <v>1.4314</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6502</v>
+        <v>1.4073</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>0.0242</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6502</v>
+        <v>0.1567</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6502</v>
+        <v>-0.6414</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>0.7982</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6502</v>
+        <v>1.146</v>
       </c>
       <c r="K6" t="n">
-        <v>0.6502</v>
+        <v>0.4118</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>0.7342</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>-0.9893</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>-1.0532</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>0.064</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>0.5498</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-0.1833</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>0.733</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>0.0914</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>0.1226</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>-0.0311</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.6335</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.3219</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>0.3115</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>L. RODRIGUEZ CAMPIÑA</t>
+          <t>D. MUÑOZ TORREGROSA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,31 +955,31 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6251</v>
+        <v>0.6502</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6251</v>
+        <v>0.6502</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6251</v>
+        <v>0.6502</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>0.6502</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6251</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6251</v>
+        <v>0.6502</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>0.6502</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6251</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. HOYAS PEREZ</t>
+          <t>L. RODRIGUEZ CAMPIÑA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5794</v>
+        <v>0.6251</v>
       </c>
       <c r="E8" t="n">
-        <v>0.6792</v>
+        <v>0.6251</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.0997</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1567</v>
+        <v>0.6251</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.6414</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7982</v>
+        <v>0.6251</v>
       </c>
       <c r="J8" t="n">
-        <v>1.146</v>
+        <v>0.6251</v>
       </c>
       <c r="K8" t="n">
-        <v>0.4118</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0.7342</v>
+        <v>0.6251</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.9893</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.0532</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>0.064</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>0.5498</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.1833</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.733</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.7606000000000001</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6056</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.155</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>0.6335</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0.3219</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0.3115</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.5234</v>
+        <v>-0.3559</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.7779</v>
+        <v>-0.5856</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2544</v>
+        <v>0.2297</v>
       </c>
       <c r="G9" t="n">
         <v>-1.1118</v>
@@ -1156,13 +1156,13 @@
         <v>0.3665</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0897</v>
+        <v>0.0779</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2202</v>
+        <v>-0.0279</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1305</v>
+        <v>0.1058</v>
       </c>
       <c r="V9" t="n">
         <v>0.3115</v>
@@ -1189,10 +1189,10 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.5679</v>
+        <v>-0.4717</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.6961000000000001</v>
+        <v>-0.5999</v>
       </c>
       <c r="F10" t="n">
         <v>0.1282</v>
@@ -1234,10 +1234,10 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0551</v>
+        <v>0.0411</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0551</v>
+        <v>0.0411</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>H. BAEZA CABRERA</t>
+          <t>L. RODRIGUEZ CAMPINA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,64 +1267,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.6075</v>
+        <v>-1.2943</v>
       </c>
       <c r="E11" t="n">
-        <v>0.2473</v>
+        <v>-4.7409</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.8548</v>
+        <v>3.4466</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.5014</v>
+        <v>-1.4134</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.3923</v>
+        <v>-1.9488</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1091</v>
+        <v>0.5354</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.1275</v>
+        <v>-2.0908</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.2108</v>
+        <v>-1.793</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0833</v>
+        <v>-0.2978</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.3739</v>
+        <v>0.6774</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.1815</v>
+        <v>-0.1558</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.1925</v>
+        <v>0.8332000000000001</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.0995</v>
+        <v>-0.733</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.0158</v>
+        <v>-2.7489</v>
       </c>
       <c r="R11" t="n">
-        <v>0.9163</v>
+        <v>2.0158</v>
       </c>
       <c r="S11" t="n">
-        <v>1.6714</v>
+        <v>0.8522</v>
       </c>
       <c r="T11" t="n">
-        <v>2.0686</v>
+        <v>0.0988</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3972</v>
+        <v>0.7534</v>
       </c>
       <c r="V11" t="n">
-        <v>0.3219</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>0.3219</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>L. RODRIGUEZ CAMPINA</t>
+          <t>A. MELGAR GARCIA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,58 +1345,58 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.2011</v>
+        <v>-1.6244</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.5486</v>
+        <v>-1.0198</v>
       </c>
       <c r="F12" t="n">
-        <v>3.3475</v>
+        <v>-0.6045</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.4134</v>
+        <v>-2.4125</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.9488</v>
+        <v>-2.1656</v>
       </c>
       <c r="I12" t="n">
-        <v>0.5354</v>
+        <v>-0.2469</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.0908</v>
+        <v>-1.1103</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.793</v>
+        <v>-0.511</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.2978</v>
+        <v>-0.5994</v>
       </c>
       <c r="M12" t="n">
-        <v>0.6774</v>
+        <v>-1.3021</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.1558</v>
+        <v>-1.6546</v>
       </c>
       <c r="O12" t="n">
-        <v>0.8332000000000001</v>
+        <v>0.3525</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.733</v>
+        <v>0.3665</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.7489</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>2.0158</v>
+        <v>0.3665</v>
       </c>
       <c r="S12" t="n">
-        <v>0.9454</v>
+        <v>0.4216</v>
       </c>
       <c r="T12" t="n">
-        <v>0.2911</v>
+        <v>0.0905</v>
       </c>
       <c r="U12" t="n">
-        <v>0.6543</v>
+        <v>0.3311</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A. MELGAR GARCIA</t>
+          <t>H. BAEZA CABRERA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,64 +1423,64 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.228</v>
+        <v>-1.8214</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.0198</v>
+        <v>-1.14</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.2082</v>
+        <v>-0.6814</v>
       </c>
       <c r="G13" t="n">
-        <v>-2.4125</v>
+        <v>-1.5014</v>
       </c>
       <c r="H13" t="n">
-        <v>-2.1656</v>
+        <v>-1.3923</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.2469</v>
+        <v>-0.1091</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.1103</v>
+        <v>-0.1275</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.511</v>
+        <v>-0.2108</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.5994</v>
+        <v>0.0833</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.3021</v>
+        <v>-1.3739</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.6546</v>
+        <v>-1.1815</v>
       </c>
       <c r="O13" t="n">
-        <v>0.3525</v>
+        <v>-0.1925</v>
       </c>
       <c r="P13" t="n">
-        <v>0.3665</v>
+        <v>-1.0995</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>-2.0158</v>
       </c>
       <c r="R13" t="n">
-        <v>0.3665</v>
+        <v>0.9163</v>
       </c>
       <c r="S13" t="n">
-        <v>0.8179</v>
+        <v>0.4576</v>
       </c>
       <c r="T13" t="n">
-        <v>0.0905</v>
+        <v>0.6814</v>
       </c>
       <c r="U13" t="n">
-        <v>0.7274</v>
+        <v>-0.2238</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>0.3219</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>0.3219</v>
       </c>
       <c r="X13" t="n">
         <v>0</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-1.9886</v>
+        <v>-1.8651</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.6896</v>
+        <v>-1.4422</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.299</v>
+        <v>-0.4229</v>
       </c>
       <c r="G14" t="n">
         <v>-1.7334</v>
@@ -1546,13 +1546,13 @@
         <v>0.733</v>
       </c>
       <c r="S14" t="n">
-        <v>0.2108</v>
+        <v>0.3343</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.0196</v>
+        <v>0.2278</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2304</v>
+        <v>0.1065</v>
       </c>
       <c r="V14" t="n">
         <v>0.6335</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-2.7408</v>
+        <v>-2.4876</v>
       </c>
       <c r="E15" t="n">
-        <v>-2.0977</v>
+        <v>-2.0426</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.6431</v>
+        <v>-0.445</v>
       </c>
       <c r="G15" t="n">
         <v>-2.3775</v>
@@ -1624,13 +1624,13 @@
         <v>0.5498</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0032</v>
+        <v>0.2564</v>
       </c>
       <c r="T15" t="n">
-        <v>0.2557</v>
+        <v>0.3107</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2525</v>
+        <v>-0.0543</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,10 +1657,10 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>15.8246</v>
+        <v>16.09979999999999</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.08880000000000088</v>
+        <v>0.1865999999999994</v>
       </c>
       <c r="F16" t="n">
         <v>15.9135</v>
@@ -1702,13 +1702,13 @@
         <v>13.7442</v>
       </c>
       <c r="S16" t="n">
-        <v>5.863199999999999</v>
+        <v>6.1388</v>
       </c>
       <c r="T16" t="n">
-        <v>1.7233</v>
+        <v>1.9988</v>
       </c>
       <c r="U16" t="n">
-        <v>4.14</v>
+        <v>4.1402</v>
       </c>
       <c r="V16" t="n">
         <v>5.4106</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.8387</v>
+        <v>2.1379</v>
       </c>
       <c r="E17" t="n">
-        <v>2.9412</v>
+        <v>2.3642</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1024</v>
+        <v>-0.2263</v>
       </c>
       <c r="G17" t="n">
         <v>2.382</v>
@@ -1780,13 +1780,13 @@
         <v>0.9163</v>
       </c>
       <c r="S17" t="n">
-        <v>0.7786999999999999</v>
+        <v>0.0779</v>
       </c>
       <c r="T17" t="n">
-        <v>1.0249</v>
+        <v>0.448</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2462</v>
+        <v>-0.3701</v>
       </c>
       <c r="V17" t="n">
         <v>-0.3219</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. CALANCHE GONZALEZ</t>
+          <t>M. CALANCHE GONZÁLEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.447</v>
+        <v>0.3251</v>
       </c>
       <c r="E18" t="n">
-        <v>1.4834</v>
+        <v>0.3251</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.0364</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>2.2449</v>
+        <v>0.3251</v>
       </c>
       <c r="H18" t="n">
-        <v>3.4984</v>
+        <v>0.3251</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.2534</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>4.1795</v>
+        <v>0.3251</v>
       </c>
       <c r="K18" t="n">
-        <v>2.8361</v>
+        <v>0.3251</v>
       </c>
       <c r="L18" t="n">
-        <v>1.3434</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.9345</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>0.6623</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>-2.5968</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.8326</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.8326</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.8321</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.552</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2801</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.9658</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.3115</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.6543</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. CALANCHE GONZÁLEZ</t>
+          <t>M. CALANCHE GONZALEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3251</v>
+        <v>0.2983</v>
       </c>
       <c r="E19" t="n">
-        <v>0.3251</v>
+        <v>1.4834</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>-1.185</v>
       </c>
       <c r="G19" t="n">
-        <v>0.3251</v>
+        <v>2.2449</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3251</v>
+        <v>3.4984</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>-1.2534</v>
       </c>
       <c r="J19" t="n">
-        <v>0.3251</v>
+        <v>4.1795</v>
       </c>
       <c r="K19" t="n">
-        <v>0.3251</v>
+        <v>2.8361</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.3434</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>-1.9345</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>0.6623</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>-2.5968</v>
       </c>
       <c r="P19" t="n">
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-1.8326</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.8326</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>-0.9808</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>-0.552</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>-0.4288</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-0.9658</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>-0.3115</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.6543</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1609</v>
+        <v>0.0809</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.4662</v>
+        <v>-0.2739</v>
       </c>
       <c r="F20" t="n">
-        <v>0.3053</v>
+        <v>0.3548</v>
       </c>
       <c r="G20" t="n">
         <v>-0.0658</v>
@@ -2014,13 +2014,13 @@
         <v>0.3665</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.4617</v>
+        <v>-0.2198</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3854</v>
+        <v>-0.1931</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.07630000000000001</v>
+        <v>-0.0268</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.4659</v>
+        <v>-0.1963</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.5108</v>
+        <v>-0.4146</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0449</v>
+        <v>0.2183</v>
       </c>
       <c r="G21" t="n">
         <v>1.0518</v>
@@ -2092,13 +2092,13 @@
         <v>0.5498</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5073</v>
+        <v>-0.2377</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4404</v>
+        <v>-0.3443</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0669</v>
+        <v>0.1065</v>
       </c>
       <c r="V21" t="n">
         <v>-0.6439</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.5033</v>
+        <v>-0.2614</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.38</v>
+        <v>-1.1877</v>
       </c>
       <c r="F22" t="n">
-        <v>0.8767</v>
+        <v>0.9262</v>
       </c>
       <c r="G22" t="n">
         <v>-0.5628</v>
@@ -2170,13 +2170,13 @@
         <v>0.9163</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.5348000000000001</v>
+        <v>-0.293</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2572</v>
+        <v>-0.0648</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2777</v>
+        <v>-0.2281</v>
       </c>
       <c r="V22" t="n">
         <v>-0.3219</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>M. LARA BARRACHINA</t>
+          <t>L. GARCIA JIMENEZ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,64 +2203,64 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.4181</v>
+        <v>-1.6184</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.6687</v>
+        <v>-1.7675</v>
       </c>
       <c r="F23" t="n">
-        <v>1.2506</v>
+        <v>0.1491</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.3094</v>
+        <v>-0.6276</v>
       </c>
       <c r="H23" t="n">
-        <v>0.986</v>
+        <v>-0.8809</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.2954</v>
+        <v>0.2532</v>
       </c>
       <c r="J23" t="n">
-        <v>0.7612</v>
+        <v>0.4108</v>
       </c>
       <c r="K23" t="n">
-        <v>0.6778</v>
+        <v>-0.9326</v>
       </c>
       <c r="L23" t="n">
-        <v>0.0833</v>
+        <v>1.3434</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.0706</v>
+        <v>-1.0385</v>
       </c>
       <c r="N23" t="n">
-        <v>0.3081</v>
+        <v>0.0517</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.3787</v>
+        <v>-1.0902</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.9163</v>
+        <v>0.1833</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.7489</v>
+        <v>-1.8326</v>
       </c>
       <c r="R23" t="n">
-        <v>1.8326</v>
+        <v>2.0158</v>
       </c>
       <c r="S23" t="n">
-        <v>0.7526</v>
+        <v>-0.5405</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3695</v>
+        <v>-0.3458</v>
       </c>
       <c r="U23" t="n">
-        <v>1.1221</v>
+        <v>-0.1948</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.945</v>
+        <v>-0.6335</v>
       </c>
       <c r="W23" t="n">
-        <v>-0.3115</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
         <v>-0.6335</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>L. GARCIA JIMENEZ</t>
+          <t>P. BALAGUER BARBA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.8384</v>
+        <v>-2.3074</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.8637</v>
+        <v>-3.4735</v>
       </c>
       <c r="F24" t="n">
-        <v>0.0252</v>
+        <v>1.1661</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.6276</v>
+        <v>-0.0567</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.8809</v>
+        <v>2.0171</v>
       </c>
       <c r="I24" t="n">
-        <v>0.2532</v>
+        <v>-2.0739</v>
       </c>
       <c r="J24" t="n">
-        <v>0.4108</v>
+        <v>-1.0486</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.9326</v>
+        <v>1.4739</v>
       </c>
       <c r="L24" t="n">
-        <v>1.3434</v>
+        <v>-2.5224</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.0385</v>
+        <v>0.9919</v>
       </c>
       <c r="N24" t="n">
-        <v>0.0517</v>
+        <v>0.5433</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.0902</v>
+        <v>0.4486</v>
       </c>
       <c r="P24" t="n">
-        <v>0.1833</v>
+        <v>-1.0995</v>
       </c>
       <c r="Q24" t="n">
         <v>-1.8326</v>
       </c>
       <c r="R24" t="n">
-        <v>2.0158</v>
+        <v>0.733</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.7606000000000001</v>
+        <v>-0.8292</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.4419</v>
+        <v>-0.5924</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.3187</v>
+        <v>-0.2368</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.6335</v>
+        <v>-0.3219</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.6335</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.2156</v>
+        <v>-2.3802</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.7682</v>
+        <v>-2.0566</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.4474</v>
+        <v>-0.3235</v>
       </c>
       <c r="G25" t="n">
         <v>1.2314</v>
@@ -2404,13 +2404,13 @@
         <v>2.1991</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.7244</v>
+        <v>-0.8889</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.2963</v>
+        <v>-0.5848</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.428</v>
+        <v>-0.3041</v>
       </c>
       <c r="V25" t="n">
         <v>-1.2566</v>
@@ -2425,7 +2425,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>P. BALAGUER BARBA</t>
+          <t>M. LARA BARRACHINA</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-2.9922</v>
+        <v>-2.6421</v>
       </c>
       <c r="E26" t="n">
-        <v>-3.762</v>
+        <v>-3.1495</v>
       </c>
       <c r="F26" t="n">
-        <v>0.7697000000000001</v>
+        <v>0.5074</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.0567</v>
+        <v>-0.3094</v>
       </c>
       <c r="H26" t="n">
-        <v>2.0171</v>
+        <v>0.986</v>
       </c>
       <c r="I26" t="n">
-        <v>-2.0739</v>
+        <v>-1.2954</v>
       </c>
       <c r="J26" t="n">
-        <v>-1.0486</v>
+        <v>0.7612</v>
       </c>
       <c r="K26" t="n">
-        <v>1.4739</v>
+        <v>0.6778</v>
       </c>
       <c r="L26" t="n">
-        <v>-2.5224</v>
+        <v>0.0833</v>
       </c>
       <c r="M26" t="n">
-        <v>0.9919</v>
+        <v>-1.0706</v>
       </c>
       <c r="N26" t="n">
-        <v>0.5433</v>
+        <v>0.3081</v>
       </c>
       <c r="O26" t="n">
-        <v>0.4486</v>
+        <v>-1.3787</v>
       </c>
       <c r="P26" t="n">
-        <v>-1.0995</v>
+        <v>-0.9163</v>
       </c>
       <c r="Q26" t="n">
-        <v>-1.8326</v>
+        <v>-2.7489</v>
       </c>
       <c r="R26" t="n">
-        <v>0.733</v>
+        <v>1.8326</v>
       </c>
       <c r="S26" t="n">
-        <v>-1.514</v>
+        <v>-0.4713</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.8808</v>
+        <v>-0.8502999999999999</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.6332</v>
+        <v>0.3789</v>
       </c>
       <c r="V26" t="n">
-        <v>-0.3219</v>
+        <v>-0.945</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>-0.3115</v>
       </c>
       <c r="X26" t="n">
-        <v>-0.3219</v>
+        <v>-0.6335</v>
       </c>
     </row>
     <row r="27">
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-9.840999999999999</v>
+        <v>-9.261200000000001</v>
       </c>
       <c r="E27" t="n">
-        <v>-8.243499999999999</v>
+        <v>-7.7628</v>
       </c>
       <c r="F27" t="n">
-        <v>-1.5975</v>
+        <v>-1.4984</v>
       </c>
       <c r="G27" t="n">
         <v>-9.247199999999999</v>
@@ -2560,13 +2560,13 @@
         <v>1.4661</v>
       </c>
       <c r="S27" t="n">
-        <v>-2.0599</v>
+        <v>-1.48</v>
       </c>
       <c r="T27" t="n">
-        <v>-1.5414</v>
+        <v>-1.0607</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.5184</v>
+        <v>-0.4193</v>
       </c>
       <c r="V27" t="n">
         <v>0</v>
@@ -2593,16 +2593,16 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-15.8246</v>
+        <v>-15.8248</v>
       </c>
       <c r="E28" t="n">
         <v>-15.9134</v>
       </c>
       <c r="F28" t="n">
-        <v>0.08870000000000022</v>
+        <v>0.0887</v>
       </c>
       <c r="G28" t="n">
-        <v>-3.6343</v>
+        <v>-3.634299999999999</v>
       </c>
       <c r="H28" t="n">
         <v>12.0734</v>
@@ -2626,7 +2626,7 @@
         <v>2.7767</v>
       </c>
       <c r="O28" t="n">
-        <v>-9.939599999999999</v>
+        <v>-9.9396</v>
       </c>
       <c r="P28" t="n">
         <v>-0.9161999999999999</v>
@@ -2638,10 +2638,10 @@
         <v>12.8281</v>
       </c>
       <c r="S28" t="n">
-        <v>-5.8635</v>
+        <v>-5.863300000000001</v>
       </c>
       <c r="T28" t="n">
-        <v>-4.140000000000001</v>
+        <v>-4.1402</v>
       </c>
       <c r="U28" t="n">
         <v>-1.7234</v>
